--- a/data/pack/us/harina_soja.xlsx
+++ b/data/pack/us/harina_soja.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,11 +512,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>337.9</v>
+        <v>332.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>332.7</v>
+        <v>336</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>336</v>
+        <v>335.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>335.08</v>
+        <v>337.43</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>337.43</v>
+        <v>322.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>322.3</v>
+        <v>324.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>324.3</v>
+        <v>319.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>319.6</v>
+        <v>308.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -952,11 +952,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308.7</v>
+        <v>307.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>307.7</v>
+        <v>294.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>294.4</v>
+        <v>291.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>291.6</v>
+        <v>284.64</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>284.64</v>
+        <v>283.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>283.3</v>
+        <v>271.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>271.7</v>
+        <v>298.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1337,11 +1337,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>298.5</v>
+        <v>281.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>281.9</v>
+        <v>273.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>273.7</v>
+        <v>289.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>289.9</v>
+        <v>276.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>276.3</v>
+        <v>277.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>277.5</v>
+        <v>263.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>263.8</v>
+        <v>265.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>265.9</v>
+        <v>265.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>265.5</v>
+        <v>273.7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>273.7</v>
+        <v>280.1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>280.1</v>
+        <v>275.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>275.5</v>
+        <v>271.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>271.7</v>
+        <v>262.7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>262.7</v>
+        <v>279.2</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>279.2</v>
+        <v>283.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>283.7</v>
+        <v>277.1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>277.1</v>
+        <v>274.78</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>274.78</v>
+        <v>275.54</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>275.54</v>
+        <v>277.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>277.2</v>
+        <v>278.3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>278.3</v>
+        <v>276.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>276.2</v>
+        <v>275.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>275.5</v>
+        <v>272.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>272.3</v>
+        <v>261.9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>261.9</v>
+        <v>248.9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248.9</v>
+        <v>246.22</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2767,11 +2767,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>246.22</v>
+        <v>243.1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>243.1</v>
+        <v>244.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>244.4</v>
+        <v>239.17</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>239.17</v>
+        <v>252.87</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2987,11 +2987,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>252.87</v>
+        <v>270.38</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>270.38</v>
+        <v>282.24</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>282.24</v>
+        <v>288.42</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>288.42</v>
+        <v>285.89</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>285.89</v>
+        <v>314.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3262,11 +3262,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>314.6</v>
+        <v>319.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>319.9</v>
+        <v>300.6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>300.6</v>
+        <v>289.1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>289.1</v>
+        <v>266.48</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>266.48</v>
+        <v>261.68</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>261.68</v>
+        <v>277.08</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>277.08</v>
+        <v>301.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>301.8</v>
+        <v>300.3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>300.3</v>
+        <v>316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>316</v>
+        <v>301.6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>301.6</v>
+        <v>299.53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>299.53</v>
+        <v>290.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>290.3</v>
+        <v>291.01</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>291.01</v>
+        <v>291.4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>291.4</v>
+        <v>280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4142,11 +4142,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>287</v>
+        <v>292.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>292.8</v>
+        <v>298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>298</v>
+        <v>302.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>302.7</v>
+        <v>299.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4362,11 +4362,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>299.6</v>
+        <v>309.54</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4417,11 +4417,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>309.54</v>
+        <v>296.86</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>296.86</v>
+        <v>310.64</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4527,11 +4527,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>310.64</v>
+        <v>319.25</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>319.25</v>
+        <v>318.4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>318.4</v>
+        <v>311.3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>311.3</v>
+        <v>314.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>314.5</v>
+        <v>331.1</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4802,11 +4802,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>331.1</v>
+        <v>321.34</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>321.34</v>
+        <v>326.03</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>326.03</v>
+        <v>324.92</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>324.92</v>
+        <v>334.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>334.9</v>
+        <v>329.1</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5077,11 +5077,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>329.1</v>
+        <v>334.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5132,11 +5132,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>334.8</v>
+        <v>316.3</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>316.3</v>
+        <v>303.8</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>303.8</v>
+        <v>303.4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>303.4</v>
+        <v>309.1</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5352,11 +5352,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>309.1</v>
+        <v>308.06</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>308.06</v>
+        <v>318.41</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>318.41</v>
+        <v>323.9</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>323.9</v>
+        <v>334.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>334.5</v>
+        <v>318.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>318.9</v>
+        <v>317.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>317.9</v>
+        <v>313.7</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>313.7</v>
+        <v>324</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5847,11 +5847,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>344</v>
+        <v>351.96</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>351.96</v>
+        <v>351.8</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5957,11 +5957,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>351.8</v>
+        <v>379.08</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6012,11 +6012,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>379.08</v>
+        <v>384.14</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -6067,11 +6067,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>384.14</v>
+        <v>364.06</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>364.06</v>
+        <v>361.13</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>361.13</v>
+        <v>383.37</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/harina_soja.xlsx
+++ b/data/pack/us/harina_soja.xlsx
@@ -512,11 +512,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>332.7</v>
+        <v>336</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>336</v>
+        <v>335.08</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>335.08</v>
+        <v>337.43</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>337.43</v>
+        <v>322.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>322.3</v>
+        <v>324.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>324.3</v>
+        <v>319.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>319.6</v>
+        <v>308.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308.7</v>
+        <v>307.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -952,11 +952,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>307.7</v>
+        <v>294.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>294.4</v>
+        <v>291.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>291.6</v>
+        <v>284.64</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>284.64</v>
+        <v>283.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283.3</v>
+        <v>271.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>271.7</v>
+        <v>298.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>298.5</v>
+        <v>281.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1337,11 +1337,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>281.9</v>
+        <v>273.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>273.7</v>
+        <v>289.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>289.9</v>
+        <v>276.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>276.3</v>
+        <v>277.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>277.5</v>
+        <v>263.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>263.8</v>
+        <v>265.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>265.9</v>
+        <v>265.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>265.5</v>
+        <v>273.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>273.7</v>
+        <v>280.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>280.1</v>
+        <v>275.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>275.5</v>
+        <v>271.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>271.7</v>
+        <v>262.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>262.7</v>
+        <v>279.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>279.2</v>
+        <v>283.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>283.7</v>
+        <v>277.1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>277.1</v>
+        <v>274.78</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>274.78</v>
+        <v>275.54</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>275.54</v>
+        <v>277.2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>277.2</v>
+        <v>278.3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>278.3</v>
+        <v>276.2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>276.2</v>
+        <v>275.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>275.5</v>
+        <v>272.3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>272.3</v>
+        <v>261.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>261.9</v>
+        <v>248.9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>248.9</v>
+        <v>246.22</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>246.22</v>
+        <v>243.1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2767,11 +2767,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>243.1</v>
+        <v>244.4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>244.4</v>
+        <v>239.17</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>239.17</v>
+        <v>252.87</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>252.87</v>
+        <v>270.38</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2987,11 +2987,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>270.38</v>
+        <v>282.24</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>282.24</v>
+        <v>288.42</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>288.42</v>
+        <v>285.89</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>285.89</v>
+        <v>314.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>314.6</v>
+        <v>319.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3262,11 +3262,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>319.9</v>
+        <v>300.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>300.6</v>
+        <v>289.1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>289.1</v>
+        <v>266.48</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>266.48</v>
+        <v>261.68</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>261.68</v>
+        <v>277.08</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>277.08</v>
+        <v>301.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>301.8</v>
+        <v>300.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>300.3</v>
+        <v>316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>316</v>
+        <v>301.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>301.6</v>
+        <v>299.53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>299.53</v>
+        <v>290.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>290.3</v>
+        <v>291.01</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>291.01</v>
+        <v>291.4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>291.4</v>
+        <v>280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>287</v>
+        <v>292.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4142,11 +4142,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>292.8</v>
+        <v>298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>298</v>
+        <v>302.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>302.7</v>
+        <v>299.6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>299.6</v>
+        <v>309.54</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4362,11 +4362,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>309.54</v>
+        <v>296.86</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4417,11 +4417,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>296.86</v>
+        <v>310.64</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>310.64</v>
+        <v>319.25</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4527,11 +4527,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>319.25</v>
+        <v>318.4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>318.4</v>
+        <v>311.3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>311.3</v>
+        <v>314.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>314.5</v>
+        <v>331.1</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>331.1</v>
+        <v>321.34</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4802,11 +4802,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>321.34</v>
+        <v>326.03</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>326.03</v>
+        <v>324.92</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>324.92</v>
+        <v>334.9</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>334.9</v>
+        <v>329.1</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>329.1</v>
+        <v>334.8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5077,11 +5077,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>334.8</v>
+        <v>316.3</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5132,11 +5132,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>316.3</v>
+        <v>303.8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>303.8</v>
+        <v>303.4</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>303.4</v>
+        <v>309.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>309.1</v>
+        <v>308.06</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5352,11 +5352,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>308.06</v>
+        <v>318.41</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>318.41</v>
+        <v>323.9</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>323.9</v>
+        <v>334.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>334.5</v>
+        <v>318.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>318.9</v>
+        <v>317.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>317.9</v>
+        <v>313.7</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>313.7</v>
+        <v>324</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>344</v>
+        <v>351.96</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5847,11 +5847,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>351.96</v>
+        <v>351.8</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>351.8</v>
+        <v>379.08</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5957,11 +5957,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>379.08</v>
+        <v>384.14</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6012,11 +6012,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>384.14</v>
+        <v>364.06</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -6067,11 +6067,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>364.06</v>
+        <v>361.13</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>361.13</v>
+        <v>383.37</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>383.37</v>
+        <v>362.8</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-20</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/harina_soja.xlsx
+++ b/data/pack/us/harina_soja.xlsx
@@ -512,11 +512,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>336</v>
+        <v>335.08</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>335.08</v>
+        <v>337.43</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>337.43</v>
+        <v>322.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>322.3</v>
+        <v>324.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>324.3</v>
+        <v>319.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>319.6</v>
+        <v>308.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308.7</v>
+        <v>307.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>307.7</v>
+        <v>294.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -952,11 +952,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>294.4</v>
+        <v>291.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>291.6</v>
+        <v>284.64</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>284.64</v>
+        <v>283.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283.3</v>
+        <v>271.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>271.7</v>
+        <v>298.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>298.5</v>
+        <v>281.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>281.9</v>
+        <v>273.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1337,11 +1337,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>273.7</v>
+        <v>289.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>289.9</v>
+        <v>276.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>276.3</v>
+        <v>277.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>277.5</v>
+        <v>263.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>263.8</v>
+        <v>265.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>265.9</v>
+        <v>265.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>265.5</v>
+        <v>273.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>273.7</v>
+        <v>280.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>280.1</v>
+        <v>275.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>275.5</v>
+        <v>271.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>271.7</v>
+        <v>262.7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>262.7</v>
+        <v>279.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>279.2</v>
+        <v>283.7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283.7</v>
+        <v>277.1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>277.1</v>
+        <v>274.78</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>274.78</v>
+        <v>275.54</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>275.54</v>
+        <v>277.2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>277.2</v>
+        <v>278.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>278.3</v>
+        <v>276.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>276.2</v>
+        <v>275.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>275.5</v>
+        <v>272.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>272.3</v>
+        <v>261.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>261.9</v>
+        <v>248.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>248.9</v>
+        <v>246.22</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>246.22</v>
+        <v>243.1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>243.1</v>
+        <v>244.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2767,11 +2767,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>244.4</v>
+        <v>239.17</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>239.17</v>
+        <v>252.87</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>252.87</v>
+        <v>270.38</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>270.38</v>
+        <v>282.24</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2987,11 +2987,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>282.24</v>
+        <v>288.42</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>288.42</v>
+        <v>285.89</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>285.89</v>
+        <v>314.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>314.6</v>
+        <v>319.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>319.9</v>
+        <v>300.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3262,11 +3262,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>300.6</v>
+        <v>289.1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>289.1</v>
+        <v>266.48</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>266.48</v>
+        <v>261.68</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>261.68</v>
+        <v>277.08</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>277.08</v>
+        <v>301.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>301.8</v>
+        <v>300.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>300.3</v>
+        <v>316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>316</v>
+        <v>301.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>301.6</v>
+        <v>299.53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>299.53</v>
+        <v>290.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>290.3</v>
+        <v>291.01</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>291.01</v>
+        <v>291.4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>291.4</v>
+        <v>280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>287</v>
+        <v>292.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>292.8</v>
+        <v>298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4142,11 +4142,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>298</v>
+        <v>302.7</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>302.7</v>
+        <v>299.6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>299.6</v>
+        <v>309.54</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>309.54</v>
+        <v>296.86</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4362,11 +4362,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>296.86</v>
+        <v>310.64</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4417,11 +4417,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>310.64</v>
+        <v>319.25</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>319.25</v>
+        <v>318.4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4527,11 +4527,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>318.4</v>
+        <v>311.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>311.3</v>
+        <v>314.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>314.5</v>
+        <v>331.1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>331.1</v>
+        <v>321.34</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>321.34</v>
+        <v>326.03</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4802,11 +4802,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>326.03</v>
+        <v>324.92</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>324.92</v>
+        <v>334.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>334.9</v>
+        <v>329.1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>329.1</v>
+        <v>334.8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>334.8</v>
+        <v>316.3</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5077,11 +5077,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>316.3</v>
+        <v>303.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5132,11 +5132,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>303.8</v>
+        <v>303.4</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>303.4</v>
+        <v>309.1</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>309.1</v>
+        <v>308.06</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>308.06</v>
+        <v>318.41</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5352,11 +5352,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>318.41</v>
+        <v>323.9</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>323.9</v>
+        <v>334.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>334.5</v>
+        <v>318.9</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>318.9</v>
+        <v>317.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>317.9</v>
+        <v>313.7</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>313.7</v>
+        <v>324</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>344</v>
+        <v>351.96</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>351.96</v>
+        <v>351.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5847,11 +5847,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>351.8</v>
+        <v>379.08</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>379.08</v>
+        <v>384.14</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5957,11 +5957,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>384.14</v>
+        <v>364.06</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6012,11 +6012,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>364.06</v>
+        <v>361.13</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -6067,11 +6067,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>361.13</v>
+        <v>383.37</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>383.37</v>
+        <v>362.8</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>362.8</v>
+        <v>343.6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
